--- a/code/2/output/Q2_详细结果.xlsx
+++ b/code/2/output/Q2_详细结果.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,21 +504,21 @@
         <v>360</v>
       </c>
       <c r="G2" t="n">
-        <v>1653.853569215472</v>
+        <v>1727.318639736199</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.95254220764834</v>
+        <v>1.905100862906273</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5661017316337023</v>
+        <v>0.576644252687495</v>
       </c>
       <c r="K2" t="n">
-        <v>2717.921318091659</v>
+        <v>2777.681111242455</v>
       </c>
     </row>
     <row r="3">
@@ -549,21 +549,21 @@
         <v>360</v>
       </c>
       <c r="G3" t="n">
-        <v>1612.024508123002</v>
+        <v>2007.732659143742</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.957748064441946</v>
+        <v>3.028172589326843</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5649448745684564</v>
+        <v>0.3270727579273681</v>
       </c>
       <c r="K3" t="n">
-        <v>2677.596171184008</v>
+        <v>3382.538073838164</v>
       </c>
     </row>
     <row r="4">
@@ -574,41 +574,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U03</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BAT-A03</t>
+          <t>BAT-B01</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="G4" t="n">
-        <v>1906.846694223541</v>
+        <v>1923.801400652132</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>S001→S009</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.315092664282421</v>
+        <v>2.755237906410259</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4855349634927952</v>
+        <v>0.3111905233974352</v>
       </c>
       <c r="K4" t="n">
-        <v>3075.651241682907</v>
+        <v>3784.404493429911</v>
       </c>
     </row>
     <row r="5">
@@ -619,41 +619,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BAT-A04</t>
+          <t>BAT-B02</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>330</v>
+        <v>390</v>
       </c>
       <c r="G5" t="n">
-        <v>1163.535862069534</v>
+        <v>1868.598447869043</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.135924211540474</v>
+        <v>2.137306960043418</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7475723974354502</v>
+        <v>0.4656732599891455</v>
       </c>
       <c r="K5" t="n">
-        <v>1991.691745403448</v>
+        <v>3461.431463887857</v>
       </c>
     </row>
     <row r="6">
@@ -664,41 +664,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BAT-B01</t>
+          <t>BAT-C01</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>390</v>
+        <v>480</v>
       </c>
       <c r="G6" t="n">
-        <v>1923.801400652132</v>
+        <v>2111.008126582572</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.755237906410259</v>
+        <v>5.871637935014367</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3111905233974352</v>
+        <v>0.2660452581232041</v>
       </c>
       <c r="K6" t="n">
-        <v>3784.404493429911</v>
+        <v>4534.576733982296</v>
       </c>
     </row>
     <row r="7">
@@ -709,41 +709,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BAT-B02</t>
+          <t>BAT-C02</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="G7" t="n">
-        <v>1808.598447869043</v>
+        <v>1627.426741698545</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.92225792418598</v>
+        <v>2.72848419774475</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5194355189535049</v>
+        <v>0.6589394752819062</v>
       </c>
       <c r="K7" t="n">
-        <v>3308.243548349634</v>
+        <v>3199.724545254415</v>
       </c>
     </row>
     <row r="8">
@@ -754,7 +754,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -764,31 +764,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BAT-C01</t>
+          <t>BAT-C03</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1627.426741698545</v>
       </c>
       <c r="F8" t="n">
-        <v>480</v>
+        <v>2167.426741698545</v>
       </c>
       <c r="G8" t="n">
-        <v>2111.008126582572</v>
+        <v>4107.206154519336</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S006→S007</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6.300756505912715</v>
+        <v>4.305306294305851</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2124054367609106</v>
+        <v>0.4618367132117687</v>
       </c>
       <c r="K8" t="n">
-        <v>4650.796346933932</v>
+        <v>6106.559942560503</v>
       </c>
     </row>
     <row r="9">
@@ -799,41 +799,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BAT-C02</t>
+          <t>BAT-B03</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1868.598447869043</v>
       </c>
       <c r="F9" t="n">
-        <v>540</v>
+        <v>2258.598447869043</v>
       </c>
       <c r="G9" t="n">
-        <v>2256.904118379016</v>
+        <v>3423.170687030482</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>S001→S013</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.147999094117354</v>
+        <v>1.821047284796378</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4815001132353307</v>
+        <v>0.5447381788009056</v>
       </c>
       <c r="K9" t="n">
-        <v>4213.6538730358</v>
+        <v>4878.957843775579</v>
       </c>
     </row>
     <row r="10">
@@ -844,41 +844,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U04</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BAT-A05</t>
+          <t>BAT-B04</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1163.535862069534</v>
+        <v>1923.801400652132</v>
       </c>
       <c r="F10" t="n">
-        <v>1523.535862069534</v>
+        <v>2313.801400652132</v>
       </c>
       <c r="G10" t="n">
-        <v>3418.068004469934</v>
+        <v>3434.202342111471</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>S010→S014</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.479565703531192</v>
+        <v>1.824569310107212</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4489853992152906</v>
+        <v>0.5438576724731971</v>
       </c>
       <c r="K10" t="n">
-        <v>4634.386985490057</v>
+        <v>4891.515709824596</v>
       </c>
     </row>
     <row r="11">
@@ -889,41 +889,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BAT-B03</t>
+          <t>BAT-C04</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1808.598447869043</v>
+        <v>2111.008126582572</v>
       </c>
       <c r="F11" t="n">
-        <v>2198.598447869043</v>
+        <v>2591.008126582572</v>
       </c>
       <c r="G11" t="n">
-        <v>3444.789491005658</v>
+        <v>3606.434868281117</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.77979835097455</v>
+        <v>2.926272845836499</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5550504122563624</v>
+        <v>0.6342158942704377</v>
       </c>
       <c r="K11" t="n">
-        <v>4882.702109761296</v>
+        <v>5232.300430695168</v>
       </c>
     </row>
     <row r="12">
@@ -934,7 +934,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -944,31 +944,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BAT-B04</t>
+          <t>BAT-B02</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1923.801400652132</v>
+        <v>3461.431463887857</v>
       </c>
       <c r="F12" t="n">
-        <v>2283.801400652132</v>
+        <v>3851.431463887857</v>
       </c>
       <c r="G12" t="n">
-        <v>3499.992443788747</v>
+        <v>5447.203899935757</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.656285556037802</v>
+        <v>2.882269354797722</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5859286109905496</v>
+        <v>0.2794326613005695</v>
       </c>
       <c r="K12" t="n">
-        <v>4884.382851405127</v>
+        <v>7362.853953681437</v>
       </c>
     </row>
     <row r="13">
@@ -989,31 +989,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BAT-C03</t>
+          <t>BAT-C02</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2111.008126582572</v>
+        <v>3606.434868281117</v>
       </c>
       <c r="F13" t="n">
-        <v>2591.008126582572</v>
+        <v>4116.434868281117</v>
       </c>
       <c r="G13" t="n">
-        <v>3671.872011856534</v>
+        <v>6299.748965133796</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S007→S003</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.593979284603347</v>
+        <v>6.081513975834206</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6757525894245816</v>
+        <v>0.2398107530207243</v>
       </c>
       <c r="K13" t="n">
-        <v>5207.741401436608</v>
+        <v>8780.15900025556</v>
       </c>
     </row>
     <row r="14">
@@ -1024,41 +1024,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BAT-C04</t>
+          <t>BAT-B01</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2256.904118379016</v>
+        <v>3784.404493429911</v>
       </c>
       <c r="F14" t="n">
-        <v>2736.904118379016</v>
+        <v>4144.404493429911</v>
       </c>
       <c r="G14" t="n">
-        <v>3752.330860077561</v>
+        <v>5804.647305481146</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.821078019781232</v>
+        <v>2.935636950871499</v>
       </c>
       <c r="J14" t="n">
-        <v>0.647365247527346</v>
+        <v>0.2660907622821254</v>
       </c>
       <c r="K14" t="n">
-        <v>5349.706157101645</v>
+        <v>7743.423317525461</v>
       </c>
     </row>
     <row r="15">
@@ -1069,27 +1069,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BAT-B02</t>
+          <t>BAT-C01</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3444.789491005658</v>
+        <v>4534.576733982296</v>
       </c>
       <c r="F15" t="n">
-        <v>3834.789491005658</v>
+        <v>5014.576733982296</v>
       </c>
       <c r="G15" t="n">
-        <v>5668.579696049663</v>
+        <v>7113.118170919204</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.961220224874922</v>
+        <v>6.382961122227925</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2596949437812694</v>
+        <v>0.2021298597215093</v>
       </c>
       <c r="K15" t="n">
-        <v>7618.441793495463</v>
+        <v>9675.170141522602</v>
       </c>
     </row>
     <row r="16">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1124,31 +1124,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BAT-B01</t>
+          <t>BAT-B03</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3784.404493429911</v>
+        <v>5447.203899935757</v>
       </c>
       <c r="F16" t="n">
-        <v>4144.404493429911</v>
+        <v>5837.203899935757</v>
       </c>
       <c r="G16" t="n">
-        <v>5948.194698473916</v>
+        <v>7276.778000951774</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>S005→S008</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.043673188969025</v>
+        <v>2.31090556296712</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2390817027577438</v>
+        <v>0.42227360925822</v>
       </c>
       <c r="K16" t="n">
-        <v>7933.786413693827</v>
+        <v>8944.837078237526</v>
       </c>
     </row>
     <row r="17">
@@ -1159,41 +1159,41 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BAT-C02</t>
+          <t>BAT-B04</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4213.6538730358</v>
+        <v>5804.647305481146</v>
       </c>
       <c r="F17" t="n">
-        <v>4693.6538730358</v>
+        <v>6194.647305481146</v>
       </c>
       <c r="G17" t="n">
-        <v>6649.464731148233</v>
+        <v>7637.900257104156</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S001→S005</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.991169042095013</v>
+        <v>2.042764074317357</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2511038697381234</v>
+        <v>0.4893089814206607</v>
       </c>
       <c r="K17" t="n">
-        <v>9105.406346715632</v>
+        <v>9189.764689308344</v>
       </c>
     </row>
     <row r="18">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1214,31 +1214,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BAT-C01</t>
+          <t>BAT-C04</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4650.796346933932</v>
+        <v>6299.748965133796</v>
       </c>
       <c r="F18" t="n">
-        <v>5130.796346933932</v>
+        <v>6779.748965133796</v>
       </c>
       <c r="G18" t="n">
-        <v>6955.981838401754</v>
+        <v>8885.539684988238</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S005→S004</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6.176919029891542</v>
+        <v>6.119610835432105</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2278851212635573</v>
+        <v>0.2350486455709868</v>
       </c>
       <c r="K18" t="n">
-        <v>9462.230742330714</v>
+        <v>11376.26761958443</v>
       </c>
     </row>
     <row r="19">
@@ -1249,41 +1249,41 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BAT-B03</t>
+          <t>BAT-C03</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5668.579696049663</v>
+        <v>7113.118170919204</v>
       </c>
       <c r="F19" t="n">
-        <v>6058.579696049663</v>
+        <v>7503.118170919204</v>
       </c>
       <c r="G19" t="n">
-        <v>7498.153797065679</v>
+        <v>8760.024265584154</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.31090556296712</v>
+        <v>3.780660497858989</v>
       </c>
       <c r="J19" t="n">
-        <v>0.42227360925822</v>
+        <v>0.5274174377676264</v>
       </c>
       <c r="K19" t="n">
-        <v>9166.212874351431</v>
+        <v>10617.2864837543</v>
       </c>
     </row>
     <row r="20">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1304,166 +1304,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BAT-B04</t>
+          <t>BAT-B02</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5948.194698473916</v>
+        <v>7362.853953681437</v>
       </c>
       <c r="F20" t="n">
-        <v>6338.194698473916</v>
+        <v>7752.853953681437</v>
       </c>
       <c r="G20" t="n">
-        <v>7724.284837625535</v>
+        <v>8552.484758245919</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>S001→S009</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.983189493062739</v>
+        <v>1.077172635206353</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5042026267343153</v>
+        <v>0.7307068411984117</v>
       </c>
       <c r="K20" t="n">
-        <v>9250.333617952721</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Q2T020</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>U07</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>BAT-C03</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>6649.464731148233</v>
-      </c>
-      <c r="F21" t="n">
-        <v>7189.464731148233</v>
-      </c>
-      <c r="G21" t="n">
-        <v>9657.611941184954</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>S011→S005→S008</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>6.26201818202476</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.217247727246905</v>
-      </c>
-      <c r="K21" t="n">
-        <v>12186.90853214999</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Q2T021</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>U08</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>BAT-C04</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>6955.981838401754</v>
-      </c>
-      <c r="F22" t="n">
-        <v>7315.981838401754</v>
-      </c>
-      <c r="G22" t="n">
-        <v>9127.792696514189</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>4.836361472986693</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.3954548158766633</v>
-      </c>
-      <c r="K22" t="n">
-        <v>11270.97392878142</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Q2T022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>U06</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>BAT-B02</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>7618.441793495463</v>
-      </c>
-      <c r="F23" t="n">
-        <v>7978.441793495463</v>
-      </c>
-      <c r="G23" t="n">
-        <v>9378.331835361238</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>S002</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.368652228709546</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.4078369428226136</v>
-      </c>
-      <c r="K23" t="n">
-        <v>11071.41446780204</v>
+        <v>9685.926233502005</v>
       </c>
     </row>
   </sheetData>
@@ -1544,7 +1409,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>879.3591246028506</v>
+        <v>1314.898370849273</v>
       </c>
       <c r="E2" t="n">
         <v>7200</v>
@@ -1576,7 +1441,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1278.898370849273</v>
+        <v>1314.898370849273</v>
       </c>
       <c r="E3" t="n">
         <v>7200</v>
@@ -1608,7 +1473,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1278.898370849273</v>
+        <v>6662.949574645848</v>
       </c>
       <c r="E4" t="n">
         <v>7200</v>
@@ -1640,7 +1505,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1278.898370849273</v>
+        <v>3293.906497431844</v>
       </c>
       <c r="E5" t="n">
         <v>10800</v>
@@ -1672,7 +1537,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1278.898370849273</v>
+        <v>1314.898370849273</v>
       </c>
       <c r="E6" t="n">
         <v>10800</v>
@@ -1704,7 +1569,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3439.802489228288</v>
+        <v>1314.898370849273</v>
       </c>
       <c r="E7" t="n">
         <v>3600</v>
@@ -1739,7 +1604,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1278.898370849273</v>
+        <v>1314.898370849273</v>
       </c>
       <c r="E8" t="n">
         <v>3600</v>
@@ -1774,7 +1639,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3439.802489228288</v>
+        <v>3293.906497431844</v>
       </c>
       <c r="E9" t="n">
         <v>3600</v>
@@ -1809,7 +1674,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1278.898370849273</v>
+        <v>3293.906497431844</v>
       </c>
       <c r="E10" t="n">
         <v>3600</v>
@@ -1841,7 +1706,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6806.496967638618</v>
+        <v>3293.906497431844</v>
       </c>
       <c r="E11" t="n">
         <v>3600</v>
@@ -1850,10 +1715,10 @@
         <v>12</v>
       </c>
       <c r="H11" t="n">
-        <v>3206.496967638618</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>10.68832322546206</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1873,7 +1738,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3439.802489228288</v>
+        <v>1314.898370849273</v>
       </c>
       <c r="E12" t="n">
         <v>3600</v>
@@ -1905,7 +1770,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3439.802489228288</v>
+        <v>1314.898370849273</v>
       </c>
       <c r="E13" t="n">
         <v>3600</v>
@@ -1937,7 +1802,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1278.898370849273</v>
+        <v>3293.906497431844</v>
       </c>
       <c r="E14" t="n">
         <v>3600</v>
@@ -1969,7 +1834,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3439.802489228288</v>
+        <v>1314.898370849273</v>
       </c>
       <c r="E15" t="n">
         <v>3600</v>
@@ -2001,7 +1866,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3439.802489228288</v>
+        <v>3293.906497431844</v>
       </c>
       <c r="E16" t="n">
         <v>3600</v>
@@ -2033,7 +1898,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8780.32681442835</v>
+        <v>1285.806329571871</v>
       </c>
       <c r="E17" t="n">
         <v>7200</v>
@@ -2042,10 +1907,10 @@
         <v>10</v>
       </c>
       <c r="H17" t="n">
-        <v>1580.32681442835</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2.194898353372709</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2097,7 +1962,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8780.32681442835</v>
+        <v>1488.914063291286</v>
       </c>
       <c r="E19" t="n">
         <v>10800</v>
@@ -2199,7 +2064,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1488.914063291286</v>
+        <v>1285.806329571871</v>
       </c>
       <c r="E22" t="n">
         <v>3600</v>
@@ -2295,7 +2160,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5859.019302092016</v>
+        <v>5509.30353607758</v>
       </c>
       <c r="E25" t="n">
         <v>10800</v>
@@ -2327,7 +2192,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5859.019302092016</v>
+        <v>5509.30353607758</v>
       </c>
       <c r="E26" t="n">
         <v>10800</v>
@@ -2359,7 +2224,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8337.347267457972</v>
+        <v>5509.30353607758</v>
       </c>
       <c r="E27" t="n">
         <v>14400</v>
@@ -2391,7 +2256,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5859.019302092016</v>
+        <v>5509.30353607758</v>
       </c>
       <c r="E28" t="n">
         <v>7200</v>
@@ -2426,7 +2291,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5859.019302092016</v>
+        <v>5072.499232788861</v>
       </c>
       <c r="E29" t="n">
         <v>7200</v>
@@ -2461,7 +2326,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5859.019302092016</v>
+        <v>5509.30353607758</v>
       </c>
       <c r="E30" t="n">
         <v>7200</v>
@@ -2493,7 +2358,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>8337.347267457972</v>
+        <v>5509.30353607758</v>
       </c>
       <c r="E31" t="n">
         <v>7200</v>
@@ -2502,10 +2367,10 @@
         <v>10</v>
       </c>
       <c r="H31" t="n">
-        <v>1137.347267457972</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1.579648982580516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2525,7 +2390,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5859.019302092016</v>
+        <v>5072.499232788861</v>
       </c>
       <c r="E32" t="n">
         <v>7200</v>
@@ -2557,7 +2422,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6236.359092667843</v>
+        <v>4765.964348578474</v>
       </c>
       <c r="E33" t="n">
         <v>10800</v>
@@ -2589,7 +2454,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6236.359092667843</v>
+        <v>8165.916939254328</v>
       </c>
       <c r="E34" t="n">
         <v>14400</v>
@@ -2621,7 +2486,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6236.359092667843</v>
+        <v>4765.964348578474</v>
       </c>
       <c r="E35" t="n">
         <v>7200</v>
@@ -2656,7 +2521,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6236.359092667843</v>
+        <v>4765.964348578474</v>
       </c>
       <c r="E36" t="n">
         <v>7200</v>
@@ -2691,7 +2556,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6236.359092667843</v>
+        <v>8165.916939254328</v>
       </c>
       <c r="E37" t="n">
         <v>7200</v>
@@ -2700,10 +2565,10 @@
         <v>10</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>965.9169392543281</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1.3415513045199</v>
       </c>
     </row>
     <row r="38">
@@ -2723,7 +2588,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6236.359092667843</v>
+        <v>8165.916939254328</v>
       </c>
       <c r="E38" t="n">
         <v>7200</v>
@@ -2732,10 +2597,10 @@
         <v>10</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>965.9169392543281</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1.3415513045199</v>
       </c>
     </row>
     <row r="39">
@@ -2755,7 +2620,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4487.058818108385</v>
+        <v>7566.406773681836</v>
       </c>
       <c r="E39" t="n">
         <v>14400</v>
@@ -2787,7 +2652,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8381.728312796085</v>
+        <v>7566.406773681836</v>
       </c>
       <c r="E40" t="n">
         <v>18000</v>
@@ -2819,7 +2684,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8381.728312796085</v>
+        <v>7161.144263334761</v>
       </c>
       <c r="E41" t="n">
         <v>10800</v>
@@ -2854,7 +2719,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8381.728312796085</v>
+        <v>7566.406773681836</v>
       </c>
       <c r="E42" t="n">
         <v>10800</v>
@@ -2889,7 +2754,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4796.673820532638</v>
+        <v>7161.144263334761</v>
       </c>
       <c r="E43" t="n">
         <v>10800</v>
@@ -2921,7 +2786,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8381.728312796085</v>
+        <v>5729.234542530336</v>
       </c>
       <c r="E44" t="n">
         <v>10800</v>
@@ -2953,7 +2818,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3320.085069219553</v>
+        <v>2896.503684335527</v>
       </c>
       <c r="E45" t="n">
         <v>7200</v>
@@ -2985,7 +2850,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3320.085069219553</v>
+        <v>2896.503684335527</v>
       </c>
       <c r="E46" t="n">
         <v>10800</v>
@@ -3017,7 +2882,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3320.085069219553</v>
+        <v>2896.503684335527</v>
       </c>
       <c r="E47" t="n">
         <v>3600</v>
@@ -3052,7 +2917,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3320.085069219553</v>
+        <v>2896.503684335527</v>
       </c>
       <c r="E48" t="n">
         <v>3600</v>
@@ -3087,7 +2952,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3320.085069219553</v>
+        <v>2896.503684335527</v>
       </c>
       <c r="E49" t="n">
         <v>3600</v>
@@ -3119,7 +2984,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3320.085069219553</v>
+        <v>2896.503684335527</v>
       </c>
       <c r="E50" t="n">
         <v>3600</v>
@@ -3151,7 +3016,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2934.33396943735</v>
+        <v>3547.425103776223</v>
       </c>
       <c r="E51" t="n">
         <v>7200</v>
@@ -3183,7 +3048,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2989.536922220439</v>
+        <v>3547.425103776223</v>
       </c>
       <c r="E52" t="n">
         <v>10800</v>
@@ -3215,7 +3080,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2934.33396943735</v>
+        <v>1141.299319868099</v>
       </c>
       <c r="E53" t="n">
         <v>3600</v>
@@ -3250,7 +3115,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2989.536922220439</v>
+        <v>1141.299319868099</v>
       </c>
       <c r="E54" t="n">
         <v>3600</v>
@@ -3285,7 +3150,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2934.33396943735</v>
+        <v>4870.135919024229</v>
       </c>
       <c r="E55" t="n">
         <v>3600</v>
@@ -3294,10 +3159,10 @@
         <v>12</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1270.135919024229</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>4.233786396747431</v>
       </c>
     </row>
     <row r="56">
@@ -3317,7 +3182,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>8953.571996475222</v>
+        <v>6409.078226209474</v>
       </c>
       <c r="E56" t="n">
         <v>10800</v>
@@ -3349,7 +3214,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>8953.571996475222</v>
+        <v>6409.078226209474</v>
       </c>
       <c r="E57" t="n">
         <v>14400</v>
@@ -3381,7 +3246,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4995.861306719164</v>
+        <v>6409.078226209474</v>
       </c>
       <c r="E58" t="n">
         <v>7200</v>
@@ -3416,7 +3281,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5275.476309143417</v>
+        <v>6409.078226209474</v>
       </c>
       <c r="E59" t="n">
         <v>7200</v>
@@ -3451,7 +3316,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4995.861306719164</v>
+        <v>6409.078226209474</v>
       </c>
       <c r="E60" t="n">
         <v>7200</v>
@@ -3483,7 +3348,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>7255.48494235198</v>
+        <v>8270.456218251678</v>
       </c>
       <c r="E61" t="n">
         <v>14400</v>
@@ -3515,7 +3380,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>7255.48494235198</v>
+        <v>8270.456218251678</v>
       </c>
       <c r="E62" t="n">
         <v>10800</v>
@@ -3550,7 +3415,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1342.668792396408</v>
+        <v>8270.456218251678</v>
       </c>
       <c r="E63" t="n">
         <v>10800</v>
@@ -3585,7 +3450,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2237.999313343937</v>
+        <v>2953.421234116429</v>
       </c>
       <c r="E64" t="n">
         <v>7200</v>
@@ -3617,7 +3482,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1104.463451274403</v>
+        <v>2953.421234116429</v>
       </c>
       <c r="E65" t="n">
         <v>3600</v>
@@ -3652,7 +3517,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1104.463451274403</v>
+        <v>2953.421234116429</v>
       </c>
       <c r="E66" t="n">
         <v>3600</v>
@@ -3687,7 +3552,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>7737.970425992323</v>
+        <v>8269.856022630343</v>
       </c>
       <c r="E67" t="n">
         <v>14400</v>
@@ -3719,7 +3584,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>7737.970425992323</v>
+        <v>8269.856022630343</v>
       </c>
       <c r="E68" t="n">
         <v>10800</v>
@@ -3754,7 +3619,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>833.9545977014336</v>
+        <v>8269.856022630343</v>
       </c>
       <c r="E69" t="n">
         <v>10800</v>
@@ -3891,7 +3756,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1778.923343694268</v>
+        <v>2986.535204715135</v>
       </c>
       <c r="E73" t="n">
         <v>7200</v>
@@ -3923,7 +3788,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1083.545587394834</v>
+        <v>2986.535204715135</v>
       </c>
       <c r="E74" t="n">
         <v>3600</v>
@@ -3958,7 +3823,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1083.545587394834</v>
+        <v>2986.535204715135</v>
       </c>
       <c r="E75" t="n">
         <v>3600</v>
@@ -3993,7 +3858,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2701.143495629256</v>
+        <v>1241.855890601188</v>
       </c>
       <c r="E76" t="n">
         <v>7200</v>
@@ -4025,7 +3890,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1181.855890601188</v>
+        <v>1241.855890601188</v>
       </c>
       <c r="E77" t="n">
         <v>7200</v>
@@ -4060,7 +3925,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1181.855890601188</v>
+        <v>1241.855890601188</v>
       </c>
       <c r="E78" t="n">
         <v>3600</v>
@@ -4095,7 +3960,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6886.806746557671</v>
+        <v>6665.430950443766</v>
       </c>
       <c r="E79" t="n">
         <v>14400</v>
@@ -4127,7 +3992,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6886.806746557671</v>
+        <v>6665.430950443766</v>
       </c>
       <c r="E80" t="n">
         <v>7200</v>
@@ -4162,7 +4027,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6886.806746557671</v>
+        <v>6665.430950443766</v>
       </c>
       <c r="E81" t="n">
         <v>10800</v>
@@ -4191,7 +4056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4259,7 +4124,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -4269,19 +4134,19 @@
         <v>0.039</v>
       </c>
       <c r="F2" t="n">
-        <v>4778.439901620956</v>
+        <v>4533.827897987505</v>
       </c>
       <c r="G2" t="n">
-        <v>307.9365356445313</v>
+        <v>384.2731750488281</v>
       </c>
       <c r="H2" t="n">
-        <v>84.03653564453123</v>
+        <v>163.4731750488281</v>
       </c>
       <c r="I2" t="n">
-        <v>534.4634512744026</v>
+        <v>571.2993198680994</v>
       </c>
       <c r="J2" t="n">
-        <v>1.070159179281298</v>
+        <v>1.045702802184405</v>
       </c>
     </row>
     <row r="3">
@@ -4292,7 +4157,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4307,19 +4172,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>4778.439901620956</v>
+        <v>4533.827897987505</v>
       </c>
       <c r="G3" t="n">
-        <v>84.03653564453123</v>
+        <v>163.4731750488281</v>
       </c>
       <c r="H3" t="n">
-        <v>307.9365356445313</v>
+        <v>384.2731750488281</v>
       </c>
       <c r="I3" t="n">
-        <v>549.3901179410693</v>
+        <v>586.0193198680994</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8823830283670421</v>
+        <v>0.8593980607218675</v>
       </c>
     </row>
     <row r="4">
@@ -4335,29 +4200,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>0.039</v>
+        <v>0.055</v>
       </c>
       <c r="F4" t="n">
-        <v>4848.706999909886</v>
+        <v>7435.278518339014</v>
       </c>
       <c r="G4" t="n">
-        <v>271.4818237304688</v>
+        <v>181.2542541503906</v>
       </c>
       <c r="H4" t="n">
-        <v>47.48182373046876</v>
+        <v>89.45425415039062</v>
       </c>
       <c r="I4" t="n">
-        <v>513.5455873948342</v>
+        <v>715.8063295718711</v>
       </c>
       <c r="J4" t="n">
-        <v>1.072401418518463</v>
+        <v>1.66612329077695</v>
       </c>
     </row>
     <row r="5">
@@ -4368,7 +4233,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4383,19 +4248,19 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4848.706999909886</v>
+        <v>7435.278518339014</v>
       </c>
       <c r="G5" t="n">
-        <v>47.48182373046876</v>
+        <v>89.45425415039062</v>
       </c>
       <c r="H5" t="n">
-        <v>271.4818237304688</v>
+        <v>181.2542541503906</v>
       </c>
       <c r="I5" t="n">
-        <v>528.4789207281675</v>
+        <v>721.9263295718711</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8853466459234836</v>
+        <v>1.362049298549894</v>
       </c>
     </row>
     <row r="6">
@@ -4411,29 +4276,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E6" t="n">
-        <v>0.055</v>
+        <v>0.067</v>
       </c>
       <c r="F6" t="n">
-        <v>3063.411326288894</v>
+        <v>7398.449561287473</v>
       </c>
       <c r="G6" t="n">
-        <v>145.3566101074219</v>
+        <v>285.6009948730469</v>
       </c>
       <c r="H6" t="n">
-        <v>89.05661010742188</v>
+        <v>133.5009948730469</v>
       </c>
       <c r="I6" t="n">
-        <v>339.3591246028506</v>
+        <v>641.8307003260658</v>
       </c>
       <c r="J6" t="n">
-        <v>0.711069639068572</v>
+        <v>1.665474368683037</v>
       </c>
     </row>
     <row r="7">
@@ -4444,72 +4309,72 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>O01</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2659.301584811751</v>
+        <v>7398.449561287473</v>
       </c>
       <c r="G7" t="n">
-        <v>109.2289123535156</v>
+        <v>133.5009948730469</v>
       </c>
       <c r="H7" t="n">
-        <v>63.22891235351562</v>
+        <v>285.6009948730469</v>
       </c>
       <c r="I7" t="n">
-        <v>283.3096677935573</v>
+        <v>651.9707003260659</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5571892835582206</v>
+        <v>1.089763537727222</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Q2T003</t>
+          <t>Q2T004</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>O01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>O01</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="F8" t="n">
-        <v>5722.680393214659</v>
+        <v>5410.917094369381</v>
       </c>
       <c r="G8" t="n">
-        <v>63.22891235351562</v>
+        <v>464.2473876953125</v>
       </c>
       <c r="H8" t="n">
-        <v>165.5289123535156</v>
+        <v>240.9473876953125</v>
       </c>
       <c r="I8" t="n">
-        <v>564.177901827133</v>
+        <v>611.8558906011879</v>
       </c>
       <c r="J8" t="n">
-        <v>1.046833741655629</v>
+        <v>1.30504407308614</v>
       </c>
     </row>
     <row r="9">
@@ -4520,72 +4385,72 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>S014</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>O01</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>S011</t>
-        </is>
-      </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2817.151725151578</v>
+        <v>5410.917094369381</v>
       </c>
       <c r="G9" t="n">
-        <v>167.6617553710938</v>
+        <v>240.9473876953125</v>
       </c>
       <c r="H9" t="n">
-        <v>83.26175537109376</v>
+        <v>464.2473876953125</v>
       </c>
       <c r="I9" t="n">
-        <v>323.9545977014336</v>
+        <v>626.7425572678545</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6067783179061954</v>
+        <v>0.8322628869572777</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Q2T004</t>
+          <t>Q2T005</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>O01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>O01</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="F10" t="n">
-        <v>2817.151725151578</v>
+        <v>7435.278518339014</v>
       </c>
       <c r="G10" t="n">
-        <v>83.26175537109376</v>
+        <v>181.2542541503906</v>
       </c>
       <c r="H10" t="n">
-        <v>167.6617553710938</v>
+        <v>89.45425415039062</v>
       </c>
       <c r="I10" t="n">
-        <v>329.5812643681003</v>
+        <v>612.9140632912859</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5291458936342788</v>
+        <v>3.560194620073078</v>
       </c>
     </row>
     <row r="11">
@@ -4596,72 +4461,72 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>S002</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>O01</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>S012</t>
-        </is>
-      </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>7398.449561287473</v>
+        <v>7435.278518339014</v>
       </c>
       <c r="G11" t="n">
-        <v>285.6009948730469</v>
+        <v>89.45425415039062</v>
       </c>
       <c r="H11" t="n">
-        <v>133.5009948730469</v>
+        <v>181.2542541503906</v>
       </c>
       <c r="I11" t="n">
-        <v>641.8307003260658</v>
+        <v>622.0940632912858</v>
       </c>
       <c r="J11" t="n">
-        <v>1.665474368683037</v>
+        <v>2.311443314941289</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Q2T005</t>
+          <t>Q2T006</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>O01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>O01</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.196</v>
       </c>
       <c r="F12" t="n">
-        <v>7398.449561287473</v>
+        <v>3063.411326288894</v>
       </c>
       <c r="G12" t="n">
-        <v>133.5009948730469</v>
+        <v>145.3566101074219</v>
       </c>
       <c r="H12" t="n">
-        <v>285.6009948730469</v>
+        <v>89.05661010742188</v>
       </c>
       <c r="I12" t="n">
-        <v>651.9707003260659</v>
+        <v>306.8983708492726</v>
       </c>
       <c r="J12" t="n">
-        <v>1.089763537727222</v>
+        <v>1.762335985609645</v>
       </c>
     </row>
     <row r="13">
@@ -4672,72 +4537,72 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>O01</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>S014</t>
-        </is>
-      </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>5410.917094369381</v>
+        <v>3063.411326288894</v>
       </c>
       <c r="G13" t="n">
-        <v>464.2473876953125</v>
+        <v>89.05661010742188</v>
       </c>
       <c r="H13" t="n">
-        <v>240.9473876953125</v>
+        <v>145.3566101074219</v>
       </c>
       <c r="I13" t="n">
-        <v>611.8558906011879</v>
+        <v>312.5283708492726</v>
       </c>
       <c r="J13" t="n">
-        <v>1.089995037228702</v>
+        <v>0.9661482121351056</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Q2T006</t>
+          <t>Q2T007</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>O01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>O01</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="F14" t="n">
-        <v>5410.917094369381</v>
+        <v>3181.033308255894</v>
       </c>
       <c r="G14" t="n">
-        <v>240.9473876953125</v>
+        <v>238.3978393554688</v>
       </c>
       <c r="H14" t="n">
-        <v>464.2473876953125</v>
+        <v>51.29783935546874</v>
       </c>
       <c r="I14" t="n">
-        <v>626.7425572678545</v>
+        <v>333.0769426369815</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8322628869572777</v>
+        <v>1.973452902459994</v>
       </c>
     </row>
     <row r="15">
@@ -4748,34 +4613,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>O01</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>0.148</v>
+        <v>0.063</v>
       </c>
       <c r="F15" t="n">
-        <v>7435.278518339014</v>
+        <v>2516.493361922941</v>
       </c>
       <c r="G15" t="n">
-        <v>181.2542541503906</v>
+        <v>275.561328125</v>
       </c>
       <c r="H15" t="n">
-        <v>89.45425415039062</v>
+        <v>241.861328125</v>
       </c>
       <c r="I15" t="n">
-        <v>612.9140632912859</v>
+        <v>398.9214194406961</v>
       </c>
       <c r="J15" t="n">
-        <v>3.989313190971426</v>
+        <v>0.8935822542060354</v>
       </c>
     </row>
     <row r="16">
@@ -4786,7 +4651,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4801,19 +4666,19 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>7435.278518339014</v>
+        <v>4533.827897987505</v>
       </c>
       <c r="G16" t="n">
-        <v>89.45425415039062</v>
+        <v>163.4731750488281</v>
       </c>
       <c r="H16" t="n">
-        <v>181.2542541503906</v>
+        <v>384.2731750488281</v>
       </c>
       <c r="I16" t="n">
-        <v>622.0940632912858</v>
+        <v>559.7810507431122</v>
       </c>
       <c r="J16" t="n">
-        <v>2.311443314941289</v>
+        <v>1.438271137639822</v>
       </c>
     </row>
     <row r="17">
@@ -4829,29 +4694,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="E17" t="n">
-        <v>0.22</v>
+        <v>0.067</v>
       </c>
       <c r="F17" t="n">
-        <v>3063.411326288894</v>
+        <v>4778.439901620956</v>
       </c>
       <c r="G17" t="n">
-        <v>145.3566101074219</v>
+        <v>307.9365356445313</v>
       </c>
       <c r="H17" t="n">
-        <v>89.05661010742188</v>
+        <v>84.03653564453123</v>
       </c>
       <c r="I17" t="n">
-        <v>306.8983708492726</v>
+        <v>454.8227862473867</v>
       </c>
       <c r="J17" t="n">
-        <v>1.680258400356131</v>
+        <v>1.117739441780633</v>
       </c>
     </row>
     <row r="18">
@@ -4862,72 +4727,72 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>O01</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>2894.253666771615</v>
+        <v>4778.439901620956</v>
       </c>
       <c r="G18" t="n">
-        <v>194.3608093261719</v>
+        <v>84.03653564453123</v>
       </c>
       <c r="H18" t="n">
-        <v>26.66080932617189</v>
+        <v>307.9365356445313</v>
       </c>
       <c r="I18" t="n">
-        <v>284.0249728449957</v>
+        <v>469.7494529140533</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9632694322467436</v>
+        <v>0.7033078430157443</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Q2T008</t>
+          <t>Q2T009</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>O01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>S013</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>O01</t>
-        </is>
-      </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="F19" t="n">
         <v>4848.706999909886</v>
       </c>
       <c r="G19" t="n">
+        <v>271.4818237304688</v>
+      </c>
+      <c r="H19" t="n">
         <v>47.48182373046876</v>
       </c>
-      <c r="H19" t="n">
-        <v>271.4818237304688</v>
-      </c>
       <c r="I19" t="n">
-        <v>477.9807746847476</v>
+        <v>432.7338040630028</v>
       </c>
       <c r="J19" t="n">
-        <v>1.50447126151448</v>
+        <v>1.120216023176074</v>
       </c>
     </row>
     <row r="20">
@@ -4938,83 +4803,83 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>S013</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>O01</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>S010</t>
-        </is>
-      </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>4778.439901620956</v>
+        <v>4848.706999909886</v>
       </c>
       <c r="G20" t="n">
-        <v>307.9365356445313</v>
+        <v>47.48182373046876</v>
       </c>
       <c r="H20" t="n">
-        <v>84.03653564453123</v>
+        <v>271.4818237304688</v>
       </c>
       <c r="I20" t="n">
-        <v>534.4634512744026</v>
+        <v>447.6671373963362</v>
       </c>
       <c r="J20" t="n">
-        <v>1.05847236123557</v>
+        <v>0.7043532869311375</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Q2T009</t>
+          <t>Q2T010</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>O01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="E21" t="n">
-        <v>0.028</v>
+        <v>0.17</v>
       </c>
       <c r="F21" t="n">
-        <v>1758.370788009778</v>
+        <v>3063.411326288894</v>
       </c>
       <c r="G21" t="n">
-        <v>185.9635681152344</v>
+        <v>145.3566101074219</v>
       </c>
       <c r="H21" t="n">
-        <v>186.5635681152344</v>
+        <v>89.05661010742188</v>
       </c>
       <c r="I21" t="n">
-        <v>283.1441822853201</v>
+        <v>306.8983708492726</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3832939400273547</v>
+        <v>1.960124633701393</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q2T009</t>
+          <t>Q2T010</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5029,25 +4894,25 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>5410.917094369381</v>
+        <v>3063.411326288894</v>
       </c>
       <c r="G22" t="n">
-        <v>240.9473876953125</v>
+        <v>89.05661010742188</v>
       </c>
       <c r="H22" t="n">
-        <v>464.2473876953125</v>
+        <v>145.3566101074219</v>
       </c>
       <c r="I22" t="n">
-        <v>716.9245088406776</v>
+        <v>312.5283708492726</v>
       </c>
       <c r="J22" t="n">
-        <v>1.037799402268268</v>
+        <v>0.9661482121351056</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Q2T010</t>
+          <t>Q2T011</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5057,7 +4922,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -5067,30 +4932,30 @@
         <v>0.067</v>
       </c>
       <c r="F23" t="n">
-        <v>4533.827897987505</v>
+        <v>7745.662441501828</v>
       </c>
       <c r="G23" t="n">
-        <v>384.2731750488281</v>
+        <v>270.5391662597656</v>
       </c>
       <c r="H23" t="n">
-        <v>163.4731750488281</v>
+        <v>169.9391662597656</v>
       </c>
       <c r="I23" t="n">
-        <v>495.7355215683075</v>
+        <v>674.5328846906167</v>
       </c>
       <c r="J23" t="n">
-        <v>1.091893114969656</v>
+        <v>1.733939933835888</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Q2T010</t>
+          <t>Q2T011</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5105,25 +4970,25 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>4533.827897987505</v>
+        <v>7745.662441501828</v>
       </c>
       <c r="G24" t="n">
-        <v>163.4731750488281</v>
+        <v>169.9391662597656</v>
       </c>
       <c r="H24" t="n">
-        <v>384.2731750488281</v>
+        <v>270.5391662597656</v>
       </c>
       <c r="I24" t="n">
-        <v>510.4555215683076</v>
+        <v>681.2395513572834</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6879052360048947</v>
+        <v>1.148329420961834</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Q2T011</t>
+          <t>Q2T012</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5137,10 +5002,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="E25" t="n">
-        <v>0.062</v>
+        <v>0.184</v>
       </c>
       <c r="F25" t="n">
         <v>4533.827897987505</v>
@@ -5152,16 +5017,16 @@
         <v>163.4731750488281</v>
       </c>
       <c r="I25" t="n">
-        <v>495.7355215683075</v>
+        <v>537.7010507431123</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9683803200329067</v>
+        <v>2.574410544820237</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Q2T011</t>
+          <t>Q2T012</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5171,29 +5036,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>O01</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.157</v>
       </c>
       <c r="F26" t="n">
-        <v>4533.827897987505</v>
+        <v>2732.82315472605</v>
       </c>
       <c r="G26" t="n">
-        <v>163.4731750488281</v>
+        <v>62.1993408203125</v>
       </c>
       <c r="H26" t="n">
-        <v>384.2731750488281</v>
+        <v>72.1993408203125</v>
       </c>
       <c r="I26" t="n">
-        <v>510.4555215683076</v>
+        <v>243.1676170533513</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6879052360048947</v>
+        <v>1.213850757466779</v>
       </c>
     </row>
     <row r="27">
@@ -5204,72 +5069,72 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>O01</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>S006</t>
-        </is>
-      </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.156</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>3181.033308255894</v>
+        <v>7261.075570364734</v>
       </c>
       <c r="G27" t="n">
-        <v>238.3978393554688</v>
+        <v>223.3041381835938</v>
       </c>
       <c r="H27" t="n">
-        <v>51.29783935546874</v>
+        <v>434.1041381835938</v>
       </c>
       <c r="I27" t="n">
-        <v>333.0769426369815</v>
+        <v>790.4454290562165</v>
       </c>
       <c r="J27" t="n">
-        <v>1.601628854868007</v>
+        <v>2.293252673547189</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Q2T012</t>
+          <t>Q2T013</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>O01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>O01</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="F28" t="n">
-        <v>3181.033308255894</v>
+        <v>7261.075570364734</v>
       </c>
       <c r="G28" t="n">
-        <v>51.29783935546874</v>
+        <v>434.1041381835938</v>
       </c>
       <c r="H28" t="n">
-        <v>238.3978393554688</v>
+        <v>223.3041381835938</v>
       </c>
       <c r="I28" t="n">
-        <v>351.7869426369815</v>
+        <v>718.094739358951</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9923504297353398</v>
+        <v>1.843406072103048</v>
       </c>
     </row>
     <row r="29">
@@ -5280,72 +5145,72 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>O01</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>S001</t>
-        </is>
-      </c>
       <c r="D29" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.147</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>3063.411326288894</v>
+        <v>7261.075570364734</v>
       </c>
       <c r="G29" t="n">
-        <v>145.3566101074219</v>
+        <v>223.3041381835938</v>
       </c>
       <c r="H29" t="n">
-        <v>89.05661010742188</v>
+        <v>434.1041381835938</v>
       </c>
       <c r="I29" t="n">
-        <v>306.8983708492726</v>
+        <v>732.1480726922844</v>
       </c>
       <c r="J29" t="n">
-        <v>1.854929807646126</v>
+        <v>1.092230878768451</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Q2T013</t>
+          <t>Q2T014</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>O01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>O01</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="F30" t="n">
-        <v>3063.411326288894</v>
+        <v>5302.020131150288</v>
       </c>
       <c r="G30" t="n">
-        <v>89.05661010742188</v>
+        <v>198.710888671875</v>
       </c>
       <c r="H30" t="n">
-        <v>145.3566101074219</v>
+        <v>131.410888671875</v>
       </c>
       <c r="I30" t="n">
-        <v>312.5283708492726</v>
+        <v>498.6578085480401</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9661482121351056</v>
+        <v>2.572624206739087</v>
       </c>
     </row>
     <row r="31">
@@ -5356,34 +5221,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>O01</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E31" t="n">
-        <v>0.067</v>
+        <v>0.129</v>
       </c>
       <c r="F31" t="n">
-        <v>5302.020131150288</v>
+        <v>3047.778454649959</v>
       </c>
       <c r="G31" t="n">
-        <v>198.710888671875</v>
+        <v>171.7871704101562</v>
       </c>
       <c r="H31" t="n">
-        <v>131.410888671875</v>
+        <v>95.88717041015627</v>
       </c>
       <c r="I31" t="n">
-        <v>472.2693271027276</v>
+        <v>319.8436836791379</v>
       </c>
       <c r="J31" t="n">
-        <v>1.191513664913419</v>
+        <v>1.288127615676499</v>
       </c>
     </row>
     <row r="32">
@@ -5394,72 +5259,72 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>O01</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>3047.778454649959</v>
+        <v>8109.473184928188</v>
       </c>
       <c r="G32" t="n">
-        <v>171.7871704101562</v>
+        <v>102.0093322753906</v>
       </c>
       <c r="H32" t="n">
-        <v>95.88717041015627</v>
+        <v>245.2093322753906</v>
       </c>
       <c r="I32" t="n">
-        <v>298.8024886107785</v>
+        <v>704.0399447097307</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5861153865481605</v>
+        <v>2.52220929981234</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Q2T014</t>
+          <t>Q2T015</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>O01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>O01</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="F33" t="n">
-        <v>8109.473184928188</v>
+        <v>6019.113948538092</v>
       </c>
       <c r="G33" t="n">
-        <v>102.0093322753906</v>
+        <v>444.0992553710938</v>
       </c>
       <c r="H33" t="n">
-        <v>245.2093322753906</v>
+        <v>97.29925537109375</v>
       </c>
       <c r="I33" t="n">
-        <v>672.718389330499</v>
+        <v>588.2270505080082</v>
       </c>
       <c r="J33" t="n">
-        <v>1.183591173413342</v>
+        <v>1.42709584923683</v>
       </c>
     </row>
     <row r="34">
@@ -5470,110 +5335,110 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>S015</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>O01</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>S005</t>
-        </is>
-      </c>
       <c r="D34" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>5302.020131150288</v>
+        <v>6019.113948538092</v>
       </c>
       <c r="G34" t="n">
-        <v>198.710888671875</v>
+        <v>97.29925537109375</v>
       </c>
       <c r="H34" t="n">
-        <v>131.410888671875</v>
+        <v>444.0992553710938</v>
       </c>
       <c r="I34" t="n">
-        <v>472.2693271027276</v>
+        <v>611.3470505080082</v>
       </c>
       <c r="J34" t="n">
-        <v>1.304421833954023</v>
+        <v>0.8838097137302899</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Q2T015</t>
+          <t>Q2T016</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>O01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E35" t="n">
-        <v>0.027</v>
+        <v>0.067</v>
       </c>
       <c r="F35" t="n">
-        <v>3047.778454649959</v>
+        <v>3063.411326288894</v>
       </c>
       <c r="G35" t="n">
-        <v>171.7871704101562</v>
+        <v>145.3566101074219</v>
       </c>
       <c r="H35" t="n">
-        <v>95.88717041015627</v>
+        <v>89.05661010742188</v>
       </c>
       <c r="I35" t="n">
-        <v>298.8024886107785</v>
+        <v>288.3022691647023</v>
       </c>
       <c r="J35" t="n">
-        <v>0.5556601816016598</v>
+        <v>0.6988394515966786</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Q2T015</t>
+          <t>Q2T016</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>O01</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="F36" t="n">
-        <v>8109.473184928188</v>
+        <v>2935.402324962604</v>
       </c>
       <c r="G36" t="n">
-        <v>102.0093322753906</v>
+        <v>132.1380004882812</v>
       </c>
       <c r="H36" t="n">
-        <v>245.2093322753906</v>
+        <v>121.1380004882812</v>
       </c>
       <c r="I36" t="n">
-        <v>672.718389330499</v>
+        <v>288.1946886889132</v>
       </c>
       <c r="J36" t="n">
-        <v>1.183591173413342</v>
+        <v>0.5541651842245976</v>
       </c>
     </row>
     <row r="37">
@@ -5584,72 +5449,72 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>S005</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>O01</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
       <c r="D37" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0.149</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>7261.075570364734</v>
+        <v>5302.020131150288</v>
       </c>
       <c r="G37" t="n">
-        <v>434.1041381835938</v>
+        <v>131.410888671875</v>
       </c>
       <c r="H37" t="n">
-        <v>223.3041381835938</v>
+        <v>198.710888671875</v>
       </c>
       <c r="I37" t="n">
-        <v>769.3654290562166</v>
+        <v>476.7559937693942</v>
       </c>
       <c r="J37" t="n">
-        <v>3.697916368547825</v>
+        <v>0.789759438496081</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Q2T016</t>
+          <t>Q2T017</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>O01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>O01</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="F38" t="n">
-        <v>7261.075570364734</v>
+        <v>5302.020131150288</v>
       </c>
       <c r="G38" t="n">
-        <v>223.3041381835938</v>
+        <v>198.710888671875</v>
       </c>
       <c r="H38" t="n">
-        <v>434.1041381835938</v>
+        <v>131.410888671875</v>
       </c>
       <c r="I38" t="n">
-        <v>790.4454290562165</v>
+        <v>498.6578085480401</v>
       </c>
       <c r="J38" t="n">
-        <v>2.293252673547189</v>
+        <v>2.677953682160432</v>
       </c>
     </row>
     <row r="39">
@@ -5660,7 +5525,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>O01</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5669,25 +5534,25 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="E39" t="n">
-        <v>0.156</v>
+        <v>0.089</v>
       </c>
       <c r="F39" t="n">
-        <v>7745.662441501828</v>
+        <v>2616.513659124485</v>
       </c>
       <c r="G39" t="n">
-        <v>270.5391662597656</v>
+        <v>170.8065795898438</v>
       </c>
       <c r="H39" t="n">
-        <v>169.9391662597656</v>
+        <v>137.5065795898437</v>
       </c>
       <c r="I39" t="n">
-        <v>709.562745733911</v>
+        <v>311.5101655724917</v>
       </c>
       <c r="J39" t="n">
-        <v>3.748680518186259</v>
+        <v>1.013418641566392</v>
       </c>
     </row>
     <row r="40">
@@ -5741,7 +5606,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -5751,19 +5616,19 @@
         <v>0.067</v>
       </c>
       <c r="F41" t="n">
-        <v>6019.113948538092</v>
+        <v>5722.680393214659</v>
       </c>
       <c r="G41" t="n">
-        <v>444.0992553710938</v>
+        <v>165.5289123535156</v>
       </c>
       <c r="H41" t="n">
-        <v>97.29925537109375</v>
+        <v>63.22891235351562</v>
       </c>
       <c r="I41" t="n">
-        <v>588.2270505080082</v>
+        <v>479.3380473324747</v>
       </c>
       <c r="J41" t="n">
-        <v>1.42709584923683</v>
+        <v>2.003108420995225</v>
       </c>
     </row>
     <row r="42">
@@ -5774,7 +5639,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5789,19 +5654,19 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>6019.113948538092</v>
+        <v>5722.680393214659</v>
       </c>
       <c r="G42" t="n">
-        <v>97.29925537109375</v>
+        <v>63.22891235351562</v>
       </c>
       <c r="H42" t="n">
-        <v>444.0992553710938</v>
+        <v>165.5289123535156</v>
       </c>
       <c r="I42" t="n">
-        <v>611.3470505080082</v>
+        <v>489.5680473324746</v>
       </c>
       <c r="J42" t="n">
-        <v>0.8838097137302899</v>
+        <v>1.777552076863764</v>
       </c>
     </row>
     <row r="43">
@@ -5817,7 +5682,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -5827,19 +5692,19 @@
         <v>0.067</v>
       </c>
       <c r="F43" t="n">
-        <v>3063.411326288894</v>
+        <v>2817.151725151578</v>
       </c>
       <c r="G43" t="n">
-        <v>145.3566101074219</v>
+        <v>167.6617553710938</v>
       </c>
       <c r="H43" t="n">
-        <v>89.05661010742188</v>
+        <v>83.26175537109376</v>
       </c>
       <c r="I43" t="n">
-        <v>288.3022691647023</v>
+        <v>277.0020689489073</v>
       </c>
       <c r="J43" t="n">
-        <v>0.6988394515966786</v>
+        <v>0.6542394187282041</v>
       </c>
     </row>
     <row r="44">
@@ -5850,376 +5715,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>O01</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>2659.301584811751</v>
+        <v>2817.151725151578</v>
       </c>
       <c r="G44" t="n">
-        <v>109.2289123535156</v>
+        <v>83.26175537109376</v>
       </c>
       <c r="H44" t="n">
-        <v>63.22891235351562</v>
+        <v>167.6617553710938</v>
       </c>
       <c r="I44" t="n">
-        <v>238.9879747133615</v>
+        <v>282.628735615574</v>
       </c>
       <c r="J44" t="n">
-        <v>0.4512695194781893</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Q2T019</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>S009</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>O01</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>5722.680393214659</v>
-      </c>
-      <c r="G45" t="n">
-        <v>63.22891235351562</v>
-      </c>
-      <c r="H45" t="n">
-        <v>165.5289123535156</v>
-      </c>
-      <c r="I45" t="n">
-        <v>468.7998952735554</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.8330805219878709</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Q2T020</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>O01</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>S011</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>62</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="F46" t="n">
-        <v>2817.151725151578</v>
-      </c>
-      <c r="G46" t="n">
-        <v>167.6617553710938</v>
-      </c>
-      <c r="H46" t="n">
-        <v>83.26175537109376</v>
-      </c>
-      <c r="I46" t="n">
-        <v>296.5056948440896</v>
-      </c>
-      <c r="J46" t="n">
-        <v>1.45388240081738</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Q2T020</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>S011</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>S005</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>51</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="F47" t="n">
-        <v>2812.761820122839</v>
-      </c>
-      <c r="G47" t="n">
-        <v>137.4338134765625</v>
-      </c>
-      <c r="H47" t="n">
-        <v>154.5338134765625</v>
-      </c>
-      <c r="I47" t="n">
-        <v>319.7578868037622</v>
-      </c>
-      <c r="J47" t="n">
-        <v>1.255115698039724</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Q2T020</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>S005</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>S008</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>14</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="F48" t="n">
-        <v>3047.778454649959</v>
-      </c>
-      <c r="G48" t="n">
-        <v>171.7871704101562</v>
-      </c>
-      <c r="H48" t="n">
-        <v>95.88717041015627</v>
-      </c>
-      <c r="I48" t="n">
-        <v>319.8436836791379</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1.030810783355317</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Q2T020</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>S008</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>O01</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>8109.473184928188</v>
-      </c>
-      <c r="G49" t="n">
-        <v>102.0093322753906</v>
-      </c>
-      <c r="H49" t="n">
-        <v>245.2093322753906</v>
-      </c>
-      <c r="I49" t="n">
-        <v>704.0399447097307</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2.52220929981234</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Q2T021</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>O01</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>20</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="F50" t="n">
-        <v>7261.075570364734</v>
-      </c>
-      <c r="G50" t="n">
-        <v>434.1041381835938</v>
-      </c>
-      <c r="H50" t="n">
-        <v>223.3041381835938</v>
-      </c>
-      <c r="I50" t="n">
-        <v>769.3654290562166</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2.543108799439505</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Q2T021</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>O01</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>7261.075570364734</v>
-      </c>
-      <c r="G51" t="n">
-        <v>223.3041381835938</v>
-      </c>
-      <c r="H51" t="n">
-        <v>434.1041381835938</v>
-      </c>
-      <c r="I51" t="n">
-        <v>790.4454290562165</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.293252673547189</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Q2T022</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>O01</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>S002</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>14</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="F52" t="n">
-        <v>7435.278518339014</v>
-      </c>
-      <c r="G52" t="n">
-        <v>181.2542541503906</v>
-      </c>
-      <c r="H52" t="n">
-        <v>89.45425415039062</v>
-      </c>
-      <c r="I52" t="n">
-        <v>591.8850209328874</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1.284463215501449</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Q2T022</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>S002</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>O01</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>7435.278518339014</v>
-      </c>
-      <c r="G53" t="n">
-        <v>89.45425415039062</v>
-      </c>
-      <c r="H53" t="n">
-        <v>181.2542541503906</v>
-      </c>
-      <c r="I53" t="n">
-        <v>598.0050209328875</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1.084189013208096</v>
+        <v>0.4229332164781491</v>
       </c>
     </row>
   </sheetData>
@@ -6255,7 +5778,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.46287056141529</v>
+        <v>6.916889005787231</v>
       </c>
     </row>
     <row r="3">
@@ -6265,7 +5788,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9657.611941184954</v>
+        <v>8885.539684988238</v>
       </c>
     </row>
     <row r="4">
@@ -6275,7 +5798,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69.75237391904898</v>
+        <v>62.91663119600512</v>
       </c>
     </row>
     <row r="5">
@@ -6285,7 +5808,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
